--- a/assets/2/db.xlsx
+++ b/assets/2/db.xlsx
@@ -54,9 +54,6 @@
     <t>Автомобиль проедет первым</t>
   </si>
   <si>
-    <t>Я должен пропустить автомбь справа</t>
-  </si>
-  <si>
     <t>Я подам сигнал рукой о повороте и поверну налево после грузовика</t>
   </si>
   <si>
@@ -144,9 +141,6 @@
     <t>В и Г</t>
   </si>
   <si>
-    <t>Винмательно посмотри на картинки. Отметь нарушителей</t>
-  </si>
-  <si>
     <t>Только Г</t>
   </si>
   <si>
@@ -162,9 +156,6 @@
     <t>Би Г</t>
   </si>
   <si>
-    <t>Этот знак относится к группе запрещающик знаков</t>
-  </si>
-  <si>
     <t>Этот знак относится к группе разрешающих знаков</t>
   </si>
   <si>
@@ -178,6 +169,15 @@
   </si>
   <si>
     <t>Этот знак называется «Движение направо»</t>
+  </si>
+  <si>
+    <t>Внимательно посмотри на картинки. Отметь нарушителей</t>
+  </si>
+  <si>
+    <t>Этот знак относится к группе запрещающих знаков</t>
+  </si>
+  <si>
+    <t>Я должен пропустить автомобиль справа</t>
   </si>
 </sst>
 </file>
@@ -573,10 +573,10 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -587,13 +587,13 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -604,13 +604,13 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -621,13 +621,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
         <v>18</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -638,13 +638,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
         <v>21</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -655,13 +655,13 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
         <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -672,13 +672,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
         <v>26</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>27</v>
-      </c>
-      <c r="F9" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -689,13 +689,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
         <v>29</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>30</v>
-      </c>
-      <c r="F10" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -706,13 +706,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -723,16 +723,16 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
         <v>35</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>36</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>37</v>
-      </c>
-      <c r="F12" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -743,16 +743,16 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
         <v>35</v>
       </c>
-      <c r="D13" t="s">
-        <v>36</v>
-      </c>
       <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" t="s">
         <v>39</v>
-      </c>
-      <c r="F13" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -763,19 +763,19 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" t="s">
         <v>41</v>
       </c>
-      <c r="D14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>36</v>
-      </c>
-      <c r="F14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -786,19 +786,19 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" t="s">
         <v>41</v>
       </c>
-      <c r="D15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" t="s">
-        <v>43</v>
-      </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -809,19 +809,19 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" t="s">
         <v>41</v>
-      </c>
-      <c r="D16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -832,19 +832,19 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" t="s">
         <v>44</v>
-      </c>
-      <c r="E17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -855,13 +855,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -872,13 +872,13 @@
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
